--- a/survey_templates/044_wedding_dj_and_lighting_quote_request_form--survey_templates.xlsx
+++ b/survey_templates/044_wedding_dj_and_lighting_quote_request_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option_8_1</t>
+          <t>option 8 1</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option_8_2</t>
+          <t>option 8 2</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_8_3</t>
+          <t>option 8 3</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_10_1</t>
+          <t>option 10 1</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_10_2</t>
+          <t>option 10 2</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_10_3</t>
+          <t>option 10 3</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_12_1</t>
+          <t>option 12 1</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_12_2</t>
+          <t>option 12 2</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_12_3</t>
+          <t>option 12 3</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_13_1</t>
+          <t>option 13 1</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option_13_2</t>
+          <t>option 13 2</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option_13_3</t>
+          <t>option 13 3</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option_14_1</t>
+          <t>option 14 1</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option_14_2</t>
+          <t>option 14 2</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option_14_3</t>
+          <t>option 14 3</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option_15_1</t>
+          <t>option 15 1</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option_15_2</t>
+          <t>option 15 2</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option_15_3</t>
+          <t>option 15 3</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option_19_1</t>
+          <t>option 19 1</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option_19_2</t>
+          <t>option 19 2</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option_19_3</t>
+          <t>option 19 3</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option_20_1</t>
+          <t>option 20 1</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option_20_2</t>
+          <t>option 20 2</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option_20_3</t>
+          <t>option 20 3</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option_26_1</t>
+          <t>option 26 1</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option_26_2</t>
+          <t>option 26 2</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option_26_3</t>
+          <t>option 26 3</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option_27_1</t>
+          <t>option 27 1</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option_27_2</t>
+          <t>option 27 2</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option_27_3</t>
+          <t>option 27 3</t>
         </is>
       </c>
     </row>
